--- a/artfynd/A 37730-2025 artfynd.xlsx
+++ b/artfynd/A 37730-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>138119</v>
+        <v>100109282</v>
       </c>
       <c r="B2" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>81097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>245</v>
+        <v>2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Blek kryptolav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Absconditella delutula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>(Nyl.) Coppins &amp; H.Kilias</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Simonstorps k:a SSO, 350 m, Ög</t>
+          <t>Simonstorps skogskyrkogård, SÖ muren, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567234.4597346875</v>
+        <v>567355</v>
       </c>
       <c r="R2" t="n">
-        <v>6515957.541687327</v>
+        <v>6515690</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,34 +741,19 @@
           <t>Simonstorp</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>E-Nor-0046</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-08-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>76AR</t>
+          <t>På grov asplåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,37 +762,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>E-län Floraväktarna</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mårten Johansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117824737</v>
+        <v>138119</v>
       </c>
       <c r="B3" t="n">
-        <v>108708</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,20 +814,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bolen, Ög</t>
+          <t>Simonstorps k:a SSO, 350 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567212</v>
+        <v>567234</v>
       </c>
       <c r="R3" t="n">
-        <v>6515933</v>
+        <v>6515958</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,14 +853,24 @@
           <t>Simonstorp</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>E-Nor-0046</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2005-08-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2005-08-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>76AR</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,27 +885,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>E-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Sandberg, Daniel Ringlund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Mårten Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117824717</v>
+        <v>118304909</v>
       </c>
       <c r="B4" t="n">
-        <v>100988</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,37 +912,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221223</v>
+        <v>245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bolen, Ög</t>
+          <t>Simonstorp, Stora Brevik, 35 m O vägskälet, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567212</v>
+        <v>567252</v>
       </c>
       <c r="R4" t="n">
-        <v>6515933</v>
+        <v>6515890</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,12 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,31 +991,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>ängsartad vägkant mot blandskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Sandberg, Daniel Ringlund</t>
+          <t>Anders Svenson, Tommy Nilsson, Jimmie Rundberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118304909</v>
+        <v>122748182</v>
       </c>
       <c r="B5" t="n">
-        <v>106378</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,46 +1023,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>245</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Simonstorp, Stora Brevik, 35 m O vägskälet, Ög</t>
+          <t>Jenberget NÖ, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567252</v>
+        <v>567375</v>
       </c>
       <c r="R5" t="n">
-        <v>6515890</v>
+        <v>6515692</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,12 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,36 +1093,30 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>ängsartad vägkant mot blandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Svenson, Tommy Nilsson, Jimmie Rundberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120471192</v>
+        <v>122747902</v>
       </c>
       <c r="B6" t="n">
-        <v>5019</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,39 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101608</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asppraktbagge</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecilonota variolosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Paykull, 1799)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Simonstorp, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567297</v>
+        <v>567187</v>
       </c>
       <c r="R6" t="n">
-        <v>6515938</v>
+        <v>6516037</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,24 +1181,9 @@
           <t>2024-10-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På solbelyst äldre grovbarkig asp. Lövrikt parti i ca 90 årig tallskog. Beteshistorik.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,27 +1198,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747900</v>
+        <v>122748184</v>
       </c>
       <c r="B7" t="n">
-        <v>92273</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,34 +1225,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bräntkläppen N, Ög</t>
+          <t>Jenberget NÖ, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567187</v>
+        <v>567233</v>
       </c>
       <c r="R7" t="n">
-        <v>6516019</v>
+        <v>6515976</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,12 +1279,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,43 +1309,38 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122748183</v>
+        <v>122748185</v>
       </c>
       <c r="B8" t="n">
-        <v>100636</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567242</v>
+        <v>567236</v>
       </c>
       <c r="R8" t="n">
-        <v>6515954</v>
+        <v>6515994</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,21 +1410,16 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122748185</v>
+        <v>122747900</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1427,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jenberget NÖ, Ög</t>
+          <t>Bräntkläppen N, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567236</v>
+        <v>567187</v>
       </c>
       <c r="R9" t="n">
-        <v>6515994</v>
+        <v>6516019</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,12 +1481,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,56 +1511,51 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122748184</v>
+        <v>122747903</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5471</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>101377</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Jenberget NÖ, Ög</t>
+          <t>Källan N, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567233</v>
+        <v>567228</v>
       </c>
       <c r="R10" t="n">
-        <v>6515976</v>
+        <v>6516034</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,12 +1582,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spår in asplåga som hänger kvar i stubben. Ca 14 cm i diameter.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1665,21 +1617,16 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747902</v>
+        <v>117824737</v>
       </c>
       <c r="B11" t="n">
-        <v>90977</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,37 +1634,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Bolen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567187</v>
+        <v>567212</v>
       </c>
       <c r="R11" t="n">
-        <v>6516037</v>
+        <v>6515933</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1741,12 +1688,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,69 +1708,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Amanda Sandberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Amanda Sandberg, Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747903</v>
+        <v>117824717</v>
       </c>
       <c r="B12" t="n">
-        <v>5465</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102225</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101377</v>
+        <v>221223</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källan N, Ög</t>
+          <t>Bolen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567228</v>
+        <v>567212</v>
       </c>
       <c r="R12" t="n">
-        <v>6516034</v>
+        <v>6515933</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1847,17 +1785,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spår in asplåga som hänger kvar i stubben. Ca 14 cm i diameter.</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,17 +1805,114 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Amanda Sandberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Amanda Sandberg, Daniel Ringlund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122748183</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jenberget NÖ, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>567242</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6515954</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 37730-2025 artfynd.xlsx
+++ b/artfynd/A 37730-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100109282</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/138119</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118304909</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122748182</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747902</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122748184</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122748185</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747900</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747903</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117824737</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117824717</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1915,8 +1975,27 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122748183</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>